--- a/2026-2027/BoxScores/February.xlsx
+++ b/2026-2027/BoxScores/February.xlsx
@@ -8,16 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\NHLStats\2026-2027\BoxScores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{874C2CE6-2A62-4C2D-AE98-C93A5BC070D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{281D5F86-B13A-4B50-B5C4-322A135CE4AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="1590" windowWidth="38640" windowHeight="15720" xr2:uid="{7901B5C0-98B5-4042-9E0B-86E022D78A84}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="1" r:id="rId1"/>
-    <sheet name="Teams" sheetId="2" r:id="rId2"/>
-    <sheet name="Scores Template" sheetId="3" r:id="rId3"/>
-    <sheet name="Offense (10-4-24)" sheetId="5" r:id="rId4"/>
-    <sheet name="Goalies (10-4-24)" sheetId="4" r:id="rId5"/>
+    <sheet name="Scores Template" sheetId="3" r:id="rId2"/>
+    <sheet name="Offense (10-4-24)" sheetId="5" r:id="rId3"/>
+    <sheet name="Goalies (10-4-24)" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="95">
   <si>
     <t>Winnipeg Jets</t>
   </si>
@@ -132,30 +131,9 @@
     <t>Boston Bruins</t>
   </si>
   <si>
-    <t>Arizona Coyotes</t>
-  </si>
-  <si>
     <t>Anaheim Ducks</t>
   </si>
   <si>
-    <t xml:space="preserve">Pacific </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Central </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metropolitan </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Atlantic </t>
-  </si>
-  <si>
-    <t>Western Conference</t>
-  </si>
-  <si>
-    <t>Eastern Conference</t>
-  </si>
-  <si>
     <t>Goalies</t>
   </si>
   <si>
@@ -343,6 +321,9 @@
   </si>
   <si>
     <t>February</t>
+  </si>
+  <si>
+    <t>Utah Mammoth</t>
   </si>
 </sst>
 </file>
@@ -567,7 +548,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -578,9 +559,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -623,19 +601,16 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -976,7 +951,7 @@
   <dimension ref="A1:AA32"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.5546875" style="18" customWidth="1"/>
+    <col min="1" max="1" width="14.5546875" style="17" customWidth="1"/>
     <col min="2" max="2" width="16.5546875" style="1" customWidth="1"/>
     <col min="3" max="26" width="9.109375" style="1"/>
     <col min="27" max="27" width="21.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -985,242 +960,242 @@
   <sheetData>
     <row r="1" spans="1:27" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="19" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="B1" s="20"/>
       <c r="AA1" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:27" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
-        <v>76</v>
+      <c r="A2" s="14" t="s">
+        <v>69</v>
       </c>
       <c r="B2" s="3"/>
       <c r="AA2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A3" s="16" t="s">
-        <v>77</v>
+      <c r="A3" s="15" t="s">
+        <v>70</v>
       </c>
       <c r="B3" s="2"/>
       <c r="AA3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A4" s="16" t="s">
-        <v>78</v>
+      <c r="A4" s="15" t="s">
+        <v>71</v>
       </c>
       <c r="B4" s="2"/>
       <c r="AA4" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A5" s="16" t="s">
-        <v>79</v>
+      <c r="A5" s="15" t="s">
+        <v>72</v>
       </c>
       <c r="B5" s="2"/>
       <c r="AA5" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A6" s="16" t="s">
-        <v>80</v>
+      <c r="A6" s="15" t="s">
+        <v>73</v>
       </c>
       <c r="B6" s="2"/>
       <c r="AA6" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A7" s="16" t="s">
-        <v>81</v>
+      <c r="A7" s="15" t="s">
+        <v>74</v>
       </c>
       <c r="B7" s="2"/>
       <c r="AA7" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A8" s="16" t="s">
-        <v>82</v>
+      <c r="A8" s="15" t="s">
+        <v>75</v>
       </c>
       <c r="B8" s="2"/>
       <c r="AA8" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A9" s="16" t="s">
-        <v>83</v>
+      <c r="A9" s="15" t="s">
+        <v>76</v>
       </c>
       <c r="B9" s="2"/>
       <c r="AA9" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A10" s="16" t="s">
-        <v>84</v>
+      <c r="A10" s="15" t="s">
+        <v>77</v>
       </c>
       <c r="B10" s="2"/>
       <c r="AA10" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A11" s="16" t="s">
-        <v>85</v>
+      <c r="A11" s="15" t="s">
+        <v>78</v>
       </c>
       <c r="B11" s="2"/>
       <c r="AA11" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A12" s="16" t="s">
-        <v>86</v>
+      <c r="A12" s="15" t="s">
+        <v>79</v>
       </c>
       <c r="B12" s="2"/>
       <c r="AA12" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A13" s="16" t="s">
-        <v>87</v>
+      <c r="A13" s="15" t="s">
+        <v>80</v>
       </c>
       <c r="B13" s="2"/>
       <c r="AA13" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A14" s="16" t="s">
-        <v>88</v>
+      <c r="A14" s="15" t="s">
+        <v>81</v>
       </c>
       <c r="B14" s="2"/>
       <c r="AA14" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A15" s="16" t="s">
-        <v>89</v>
+      <c r="A15" s="15" t="s">
+        <v>82</v>
       </c>
       <c r="B15" s="2"/>
       <c r="AA15" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A16" s="16" t="s">
-        <v>90</v>
+      <c r="A16" s="15" t="s">
+        <v>83</v>
       </c>
       <c r="B16" s="2"/>
       <c r="AA16" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A17" s="16" t="s">
-        <v>98</v>
+      <c r="A17" s="15" t="s">
+        <v>91</v>
       </c>
       <c r="B17" s="2"/>
       <c r="AA17" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A18" s="16" t="s">
-        <v>91</v>
+      <c r="A18" s="15" t="s">
+        <v>84</v>
       </c>
       <c r="B18" s="2"/>
       <c r="AA18" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A19" s="16" t="s">
-        <v>92</v>
+      <c r="A19" s="15" t="s">
+        <v>85</v>
       </c>
       <c r="B19" s="2"/>
       <c r="AA19" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A20" s="16" t="s">
-        <v>93</v>
+      <c r="A20" s="15" t="s">
+        <v>86</v>
       </c>
       <c r="B20" s="2"/>
       <c r="AA20" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A21" s="16" t="s">
-        <v>94</v>
+      <c r="A21" s="15" t="s">
+        <v>87</v>
       </c>
       <c r="B21" s="2"/>
       <c r="AA21" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A22" s="16" t="s">
-        <v>95</v>
+      <c r="A22" s="15" t="s">
+        <v>88</v>
       </c>
       <c r="B22" s="2"/>
       <c r="AA22" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A23" s="16" t="s">
-        <v>99</v>
+      <c r="A23" s="15" t="s">
+        <v>92</v>
       </c>
       <c r="B23" s="2"/>
       <c r="AA23" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A24" s="16" t="s">
-        <v>96</v>
+      <c r="A24" s="15" t="s">
+        <v>89</v>
       </c>
       <c r="B24" s="2"/>
       <c r="AA24" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="B25" s="23"/>
+      <c r="A25" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="B25" s="18"/>
       <c r="AA25" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:27" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="AA26" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.3">
       <c r="AA27" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.3">
       <c r="AA28" s="1" t="s">
-        <v>4</v>
+        <v>94</v>
       </c>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.3">
@@ -1254,223 +1229,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0148CC85-F753-4FD2-B9F3-A5962DDFE417}">
-  <dimension ref="A1:O56"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="2" width="21.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="9.109375" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="D1" s="21"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="40" spans="10:15" x14ac:dyDescent="0.3">
-      <c r="O40" s="4"/>
-    </row>
-    <row r="41" spans="10:15" x14ac:dyDescent="0.3">
-      <c r="O41" s="4"/>
-    </row>
-    <row r="42" spans="10:15" x14ac:dyDescent="0.3">
-      <c r="O42" s="4"/>
-    </row>
-    <row r="43" spans="10:15" x14ac:dyDescent="0.3">
-      <c r="O43" s="4"/>
-    </row>
-    <row r="44" spans="10:15" x14ac:dyDescent="0.3">
-      <c r="O44" s="4"/>
-    </row>
-    <row r="45" spans="10:15" x14ac:dyDescent="0.3">
-      <c r="K45" s="4"/>
-      <c r="O45" s="4"/>
-    </row>
-    <row r="46" spans="10:15" x14ac:dyDescent="0.3">
-      <c r="K46" s="4"/>
-      <c r="O46" s="4"/>
-    </row>
-    <row r="47" spans="10:15" x14ac:dyDescent="0.3">
-      <c r="J47" s="4"/>
-      <c r="K47" s="4"/>
-      <c r="O47" s="4"/>
-    </row>
-    <row r="49" spans="10:15" x14ac:dyDescent="0.3">
-      <c r="O49" s="4"/>
-    </row>
-    <row r="50" spans="10:15" x14ac:dyDescent="0.3">
-      <c r="K50" s="4"/>
-      <c r="O50" s="4"/>
-    </row>
-    <row r="51" spans="10:15" x14ac:dyDescent="0.3">
-      <c r="O51" s="4"/>
-    </row>
-    <row r="52" spans="10:15" x14ac:dyDescent="0.3">
-      <c r="J52" s="4"/>
-      <c r="O52" s="4"/>
-    </row>
-    <row r="53" spans="10:15" x14ac:dyDescent="0.3">
-      <c r="J53" s="4"/>
-      <c r="K53" s="4"/>
-      <c r="O53" s="4"/>
-    </row>
-    <row r="54" spans="10:15" x14ac:dyDescent="0.3">
-      <c r="J54" s="4"/>
-      <c r="O54" s="4"/>
-    </row>
-    <row r="55" spans="10:15" x14ac:dyDescent="0.3">
-      <c r="J55" s="4"/>
-      <c r="K55" s="4"/>
-      <c r="O55" s="4"/>
-    </row>
-    <row r="56" spans="10:15" x14ac:dyDescent="0.3">
-      <c r="J56" s="4"/>
-      <c r="K56" s="4"/>
-      <c r="O56" s="4"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82695FB2-CA88-4767-9DA7-832F5FE9DAB0}">
   <dimension ref="A1:AA19"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1483,134 +1241,134 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="5" t="s">
-        <v>45</v>
+      <c r="A1" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="4" t="s">
+        <v>38</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:27" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>41</v>
+      <c r="A2" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>34</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="11"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="10"/>
+      <c r="A3" s="10"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A4" s="9"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="8"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="7"/>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A5" s="9"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="8"/>
+      <c r="A5" s="8"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="7"/>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A6" s="9"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="8"/>
+      <c r="A6" s="8"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="7"/>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A7" s="9"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="8"/>
+      <c r="A7" s="8"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="7"/>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A8" s="9"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="8"/>
+      <c r="A8" s="8"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="7"/>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A9" s="9"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="8"/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="7"/>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A10" s="9"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="8"/>
+      <c r="A10" s="8"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="7"/>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A11" s="9"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="8"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="7"/>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A12" s="9"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="8"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="7"/>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A13" s="9"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="8"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="7"/>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A14" s="9"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="8"/>
+      <c r="A14" s="8"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="7"/>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A15" s="9"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="8"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="7"/>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A16" s="9"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="8"/>
+      <c r="A16" s="8"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="7"/>
     </row>
     <row r="17" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="7"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="6"/>
+      <c r="A17" s="6"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="5"/>
     </row>
     <row r="18" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
-        <v>39</v>
+      <c r="A18" s="4" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="5" t="s">
-        <v>38</v>
+      <c r="A19" s="4" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1643,7 +1401,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ED9F52C-4A3A-44E0-BBDC-950685570BE6}">
   <dimension ref="A1:U1"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1652,73 +1410,73 @@
     <col min="2" max="2" width="9.109375" style="1"/>
     <col min="3" max="3" width="22" style="1" customWidth="1"/>
     <col min="4" max="15" width="9.109375" style="1"/>
-    <col min="16" max="18" width="9.109375" style="14"/>
+    <col min="16" max="18" width="9.109375" style="13"/>
     <col min="19" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="P1" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="P1" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q1" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="R1" s="14" t="s">
-        <v>63</v>
+      <c r="Q1" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="R1" s="13" t="s">
+        <v>56</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="U1" s="5" t="s">
-        <v>48</v>
+        <v>54</v>
+      </c>
+      <c r="U1" s="4" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1730,7 +1488,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BAF5206-6C7C-473B-8F0B-07B9A3759B8D}">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1743,62 +1501,62 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>48</v>
+        <v>42</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="K2" s="13"/>
+      <c r="K2" s="12"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="K3" s="13"/>
+      <c r="K3" s="12"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="K4" s="13"/>
+      <c r="K4" s="12"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="K5" s="13"/>
+      <c r="K5" s="12"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="K6" s="13"/>
+      <c r="K6" s="12"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="K7" s="13"/>
+      <c r="K7" s="12"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/2026-2027/BoxScores/February.xlsx
+++ b/2026-2027/BoxScores/February.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
